--- a/docs/IFRS17BSL기능정의서_v2.2.xlsx
+++ b/docs/IFRS17BSL기능정의서_v2.2.xlsx
@@ -273,8 +273,8 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -747,295 +747,327 @@
       <c r="E7" s="13" t="inlineStr"/>
       <c r="F7" s="11" t="inlineStr"/>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>호출 Client 검증</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="9" t="n">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>(1) 필수 Header 의 X-Client-ID 는 필수입력값이므로 입력값이 있는지 유효성 체크한다.
+→ (2) 단계 진행</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>RequestContextResolver
+resolve(HttpServletRequest)</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>BS-VAL-001
+HTTP 400</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>미입력·공백이면 ValidationException 발생.
+이후 세부 단계·업무 처리 미수행, 실패 감사 로그 기록 후 표준 Error Response 반환</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="19" t="n"/>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>(2) 입력된 X-Client-ID 라는 Header 값이 BS_CLIENT 라는 테이블에 등록되어 있는 관리 대상인지 체크한다.
+→ 다음 프로세스 진행</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>ClientAuthenticationService
+validateClient(clientId)</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>BS-AUTH-001
+HTTP 401</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>BS_CLIENT 미등록 Client 이면 AuthenticationException 발생.
+정상 시 clientId 를 ServiceContext 에 반영하고 4단계로 진행</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>SSO 사용자 Context 추출</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="13" t="inlineStr"/>
-      <c r="F9" s="11" t="inlineStr"/>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="14" t="n">
+      <c r="C10" s="11" t="inlineStr"/>
+      <c r="D10" s="12" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr"/>
+      <c r="F10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Service Catalog에서 활성 버전 조회</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>(1) service ID 가 존재하는지
 → 존재하면 (2)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>ServiceMetadataRepository
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>미존재 시 ServiceNotFoundException 발생.
 이후 세부 단계·업무 처리 미수행, 실패 감사 로그 기록 후 표준 Error Response 반환</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="19" t="n"/>
-      <c r="B11" s="19" t="n"/>
-      <c r="C11" s="16" t="inlineStr">
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="20" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>(2) 해당 service ID의 사용여부가 "사용" 상태인지
 → 사용상태면 (3)</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>ServiceMetadataRepository
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>active_yn ≠ 'Y' 이면 ServiceNotFoundException 발생.
 운영자가 "미사용"으로 전환하면 즉시 신규 호출 차단</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="19" t="n"/>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>(3) 버전 정보가 존재하는지
-→ 존재하면 (4)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>ServiceMetadataRepository
-findActive(serviceId, version)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>BS-SVC-404
-HTTP 404</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>(service_id, version) 미존재 시 ServiceNotFoundException 발생</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
+    <row r="13" ht="46" customHeight="1">
       <c r="A13" s="20" t="n"/>
       <c r="B13" s="20" t="n"/>
       <c r="C13" s="16" t="inlineStr">
         <is>
+          <t>(3) 버전 정보가 존재하는지
+→ 존재하면 (4)</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>ServiceMetadataRepository
+findActive(serviceId, version)</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>BS-SVC-404
+HTTP 404</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>(service_id, version) 미존재 시 ServiceNotFoundException 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
           <t>(4) 조회된 버전 정보의 상태가 "사용" 상태인지
 → 사용상태면 다음 프로세스 진행</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>ServiceMetadataRepository
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>비활성 버전이면 ServiceNotFoundException 발생.
 정상 시 확정 메타데이터를 ServiceContext 에 반영하고 6단계로 진행</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="9" t="n">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>서비스/역할 권한 확인</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr"/>
-      <c r="E14" s="13" t="inlineStr"/>
-      <c r="F14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="4" t="n">
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="12" t="inlineStr"/>
+      <c r="E15" s="13" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>입력 Schema 및 업무 파라미터 검증</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="9" t="n">
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="8" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>감사 시작 로그 기록</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr"/>
-      <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr"/>
-      <c r="F16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="4" t="n">
+      <c r="C17" s="11" t="inlineStr"/>
+      <c r="D17" s="12" t="inlineStr"/>
+      <c r="E17" s="13" t="inlineStr"/>
+      <c r="F17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Business Service Handler 실행</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="7" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="9" t="n">
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="8" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Legacy Adapter를 통한 기존 Service 호출</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr"/>
-      <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="13" t="inlineStr"/>
-      <c r="F18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="C19" s="11" t="inlineStr"/>
+      <c r="D19" s="12" t="inlineStr"/>
+      <c r="E19" s="13" t="inlineStr"/>
+      <c r="F19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>결과 DTO를 표준 JSON으로 변환 및 마스킹</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="9" t="n">
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="8" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>감사 성공/실패 로그 기록</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr"/>
-      <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="13" t="inlineStr"/>
-      <c r="F20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="4" t="n">
+      <c r="C21" s="11" t="inlineStr"/>
+      <c r="D21" s="12" t="inlineStr"/>
+      <c r="E21" s="13" t="inlineStr"/>
+      <c r="F21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>표준 Response 반환</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="8" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>기입 근거</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>설계서 근거</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n"/>
-      <c r="F24" s="24" t="n"/>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>담당 컴포넌트</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="inlineStr">
-        <is>
-          <t>4.2 핵심 컴포넌트 — ServiceMetadataRepository | 서비스 버전·상태·권한·Timeout 조회 | findActive(serviceId, version)</t>
         </is>
       </c>
       <c r="C25" s="23" t="n"/>
@@ -1046,12 +1078,12 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>오류코드</t>
+          <t>3단계 · 담당 컴포넌트</t>
         </is>
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>부록 A 표준 오류코드 — BS-SVC-404 | 404 | 서비스/버전 없음 또는 비활성</t>
+          <t>4.2 핵심 컴포넌트 — RequestContextResolver | SSO/Client/Request ID/Trace 정보 생성 | resolve(HttpServletRequest)   /   10.4 공통 Executor 의사코드 — resolveContext → validateClient</t>
         </is>
       </c>
       <c r="C26" s="23" t="n"/>
@@ -1062,12 +1094,12 @@
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>예외 처리</t>
+          <t>3단계 · 오류코드</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>4.5 예외 처리 기준 — 서비스 없음/비활성 | 404 | BS-SVC-404 | Catalog 상태 확인   /   10.4 공통 Executor 의사코드 — catch … convertStandardError → writeAuditFailure → return</t>
+          <t>부록 A 표준 오류코드 — BS-VAL-001 | 400 | 필수값 누락 또는 형식 오류   /   BS-AUTH-001 | 401 | 인증 실패   /   5.2 필수 Header — X-Client-ID | Y | 호출 채널 식별</t>
         </is>
       </c>
       <c r="C27" s="23" t="n"/>
@@ -1078,12 +1110,12 @@
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>(2) 즉시 차단</t>
+          <t>3단계 · 예외 처리</t>
         </is>
       </c>
       <c r="B28" s="26" t="inlineStr">
         <is>
-          <t>8.4 서비스 등록 및 외부 공개 흐름 7항 — 사용 여부를 "미사용"으로 변경하면 즉시 신규 호출을 차단한다</t>
+          <t>4.5 예외 처리 기준 — 입력 오류 | 400 | BS-VAL-001   /   인증 실패 | 401 | BS-AUTH-001 | SSO/Client 인증 실패   /   7.2 주요 테이블 — BS_CLIENT | 호출 Client 등록 | client_id</t>
         </is>
       </c>
       <c r="C28" s="23" t="n"/>
@@ -1091,50 +1123,135 @@
       <c r="E28" s="23" t="n"/>
       <c r="F28" s="24" t="n"/>
     </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>5단계 · 담당 컴포넌트</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>4.2 핵심 컴포넌트 — ServiceMetadataRepository | 서비스 버전·상태·권한·Timeout 조회 | findActive(serviceId, version)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="24" t="n"/>
+    </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="27" t="inlineStr">
-        <is>
-          <t>※ 세부 단계 (4) 는 요청 원문의 "조회된 버전 정보의 service ID가 '사용'상태인지" 를, service ID 의 사용여부가 (2) 에서 이미 확인되는 점과 설계서 7.3 DDL 의 bs_service_version.status_code 컬럼에 근거하여 "버전의 상태" 확인으로 해석한 것이다.</t>
-        </is>
-      </c>
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>5단계 · 오류코드</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>부록 A 표준 오류코드 — BS-SVC-404 | 404 | 서비스/버전 없음 또는 비활성</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="24" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="27" t="inlineStr">
-        <is>
-          <t>※ 4개 세부 단계의 오류코드가 모두 BS-SVC-404 로 동일한 것은 부록 A 가 "서비스/버전 없음 또는 비활성" 을 단일 코드로 규정하기 때문이다. 세부 원인 구분이 필요하면 별도 정책 결정이 필요하다.</t>
-        </is>
-      </c>
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>5단계 · 예외 처리</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>4.5 예외 처리 기준 — 서비스 없음/비활성 | 404 | BS-SVC-404 | Catalog 상태 확인   /   10.4 공통 Executor 의사코드 — catch … convertStandardError → writeAuditFailure → return</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="24" t="n"/>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="27" t="inlineStr">
-        <is>
-          <t>※ Catalog 조회 중 DB 접속 실패 등 인프라 오류는 위 4개 판정 실패와 성격이 달라 BS-SYS-500(내부 시스템 오류) 대상이며, 본 표에는 포함하지 않았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="27" t="inlineStr">
-        <is>
-          <t>※ 1~4 · 6~13 단계의 세부 단계·담당 컴포넌트·오류코드·예외 처리는 후속 상세화 시 기입한다.</t>
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>5단계 (2) 즉시 차단</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="inlineStr">
+        <is>
+          <t>8.4 서비스 등록 및 외부 공개 흐름 7항 — 사용 여부를 "미사용"으로 변경하면 즉시 신규 호출을 차단한다</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="23" t="n"/>
+      <c r="F32" s="24" t="n"/>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>※ [3단계] 세부 단계 (1) 의 오류코드는 부록 A 의 BS-VAL-001(필수값 누락 또는 형식 오류) 을 적용한 것이다. 필수 Header 미입력을 인증 실패(BS-AUTH-001, 401) 로 볼지는 정책 결정이 필요하다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>※ [3단계] 담당 컴포넌트 ClientAuthenticationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 validateClient 단계를 담당할 컴포넌트로 명명한 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>※ [5단계] 세부 단계 (4) 는 요청 원문의 "조회된 버전 정보의 service ID가 '사용'상태인지" 를, service ID 의 사용여부가 (2) 에서 이미 확인되는 점과 설계서 7.3 DDL 의 bs_service_version.status_code 컬럼에 근거하여 "버전의 상태" 확인으로 해석한 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>※ [5단계] 4개 세부 단계의 오류코드가 모두 BS-SVC-404 로 동일한 것은 부록 A 가 "서비스/버전 없음 또는 비활성" 을 단일 코드로 규정하기 때문이다. 세부 원인 구분이 필요하면 별도 정책 결정이 필요하다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>※ Catalog 조회 중 DB 접속 실패 등 인프라 오류는 각 단계의 판정 실패와 성격이 달라 BS-SYS-500(내부 시스템 오류) 대상이며, 본 표에는 포함하지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>※ 1~2 · 4 · 6~13 단계의 세부 단계·담당 컴포넌트·오류코드·예외 처리는 후속 상세화 시 기입한다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="21">
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="B27:F27"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B10:B13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
